--- a/Project/outputs/tables/table_regime_metrics.xlsx
+++ b/Project/outputs/tables/table_regime_metrics.xlsx
@@ -425,245 +425,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>VAR_n</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>VAR_MSE</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>VAR_RMSE</t>
+          <t>MSE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>VAR_MAPE</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>VAR_DirAcc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_n</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_MSE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_RMSE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_MAPE</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_DirAcc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_n</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_MSE</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_RMSE</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_MAPE</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_DirAcc</t>
+          <t>MAPE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VAR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>B: War-Only</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>430</v>
-      </c>
       <c r="C2" t="n">
-        <v>0.000314</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0176</v>
+        <v>0.000263</v>
       </c>
       <c r="E2" t="n">
-        <v>7.98</v>
+        <v>0.014185</v>
       </c>
       <c r="F2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="G2" t="n">
-        <v>369</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.000154</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="L2" t="n">
-        <v>369</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.000157</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.531</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VAR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C: Crisis-Only</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VAR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>D: War+Crisis</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.000896</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="G3" t="n">
-        <v>127</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.000592</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0241</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="L3" t="n">
-        <v>127</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.000693</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0258</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VAR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Full Test</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>810</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.000589</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.023554</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B: War-Only</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.000215</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.013171</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C: Crisis-Only</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D: War+Crisis</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Full Test</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>766</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000291</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.016615</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GRU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B: War-Only</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.000218</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C: Crisis-Only</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GRU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D: War+Crisis</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GRU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Full Test</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>750</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.000271</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.015937</v>
+      </c>
+      <c r="F13" t="n">
         <v>5.82</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.537</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E: Sol/COVID</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>37</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.003022</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="G4" t="n">
-        <v>37</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0393</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="L4" t="n">
-        <v>37</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.001539</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0379</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.5659999999999999</v>
       </c>
     </row>
   </sheetData>
